--- a/public/sample/가짜_상품ABC분석_2026-09.xlsx
+++ b/public/sample/가짜_상품ABC분석_2026-09.xlsx
@@ -477,10 +477,10 @@
         <v>420</v>
       </c>
       <c r="H7">
-        <v>26.25</v>
+        <v>26.47</v>
       </c>
       <c r="I7">
-        <v>26.25</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="8">
@@ -506,10 +506,10 @@
         <v>260</v>
       </c>
       <c r="H8">
-        <v>16.25</v>
+        <v>16.39</v>
       </c>
       <c r="I8">
-        <v>42.5</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="9">
@@ -535,10 +535,10 @@
         <v>180</v>
       </c>
       <c r="H9">
-        <v>11.25</v>
+        <v>11.34</v>
       </c>
       <c r="I9">
-        <v>53.75</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="10">
@@ -558,16 +558,16 @@
         <v>소주</v>
       </c>
       <c r="F10">
-        <v>2600000</v>
+        <v>2560000</v>
       </c>
       <c r="G10">
         <v>520</v>
       </c>
       <c r="H10">
-        <v>10.83</v>
+        <v>10.76</v>
       </c>
       <c r="I10">
-        <v>64.58</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="11">
@@ -593,10 +593,10 @@
         <v>150</v>
       </c>
       <c r="H11">
-        <v>10.63</v>
+        <v>10.71</v>
       </c>
       <c r="I11">
-        <v>75.21</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="12">
@@ -616,16 +616,16 @@
         <v>맥주</v>
       </c>
       <c r="F12">
-        <v>1650000</v>
+        <v>1595000</v>
       </c>
       <c r="G12">
         <v>330</v>
       </c>
       <c r="H12">
-        <v>6.88</v>
+        <v>6.7</v>
       </c>
       <c r="I12">
-        <v>82.08</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +651,10 @@
         <v>95</v>
       </c>
       <c r="H13">
-        <v>6.33</v>
+        <v>6.39</v>
       </c>
       <c r="I13">
-        <v>88.42</v>
+        <v>88.75</v>
       </c>
     </row>
     <row r="14">
@@ -680,10 +680,10 @@
         <v>310</v>
       </c>
       <c r="H14">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="I14">
-        <v>93.58</v>
+        <v>93.96</v>
       </c>
     </row>
     <row r="15">
@@ -703,16 +703,16 @@
         <v>계란찜</v>
       </c>
       <c r="F15">
-        <v>480000</v>
+        <v>440000</v>
       </c>
       <c r="G15">
         <v>120</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="I15">
-        <v>95.58</v>
+        <v>95.81</v>
       </c>
     </row>
     <row r="16">
@@ -732,16 +732,16 @@
         <v>음료수</v>
       </c>
       <c r="F16">
-        <v>420000</v>
+        <v>357000</v>
       </c>
       <c r="G16">
         <v>210</v>
       </c>
       <c r="H16">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="I16">
-        <v>97.33</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         <v>85</v>
       </c>
       <c r="H17">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I17">
-        <v>98.75</v>
+        <v>98.74</v>
       </c>
     </row>
     <row r="18">
@@ -796,7 +796,7 @@
         <v>60</v>
       </c>
       <c r="H18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -819,7 +819,7 @@
         <v/>
       </c>
       <c r="F19">
-        <v>24000000</v>
+        <v>23802000</v>
       </c>
       <c r="G19">
         <v>2740</v>
